--- a/Result/checksun_type/車燈.xlsx
+++ b/Result/checksun_type/車燈.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>139.8</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>140.65</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>135.8</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>140.65</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>135.8</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>43736273.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>53207013.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>53207013</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>61463940.0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>96252460.78</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>96252460.78</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-15365017.56325025</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>43736273</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>43736273.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>139.1</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>140.62</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>135.59</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>140.62</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>135.59</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>45136991.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>54974550.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>54974550.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>67652467.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>98193139.88</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>98193139.88</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-15321736.54413417</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>45136991</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>45136991.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>139.1</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>140.8</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>135.54</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>135.54</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>68644498.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>61039874.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>61039874.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>73906724.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>99525889.9</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>99525889.90000001</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-14862778.56882069</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>68644498</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>68644498.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>139.2</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>140.57</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>135.5</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>140.57</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>135.5</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>50221364.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>59322602.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>59322602</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>78563650.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>99720228.72</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>99720228.72</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-16194972.26234356</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>50221364</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>50221364.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>139.5</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>140.52</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>135.51</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>140.52</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>135.51</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>58295939.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>67281019.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>67281019.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>82547051.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>99323817.4</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>99323817.40000001</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-15545807.02943537</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>58295939</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>58295939.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>139.6</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>140.35</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>135.54</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>140.35</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>135.54</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>52573959.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>69720867.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>69720867</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>91864810.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>98697682.48</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>98697682.48</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-14928353.7670867</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>52573959</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>52573959.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>140.4</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>140.18</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>135.63</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>140.18</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>135.63</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>75463611.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>80330384.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>80330384.59999999</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>119580550.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>98750305.68</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>98750305.68000001</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-12900052.90062122</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>75463611</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>75463611.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>140.6</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>139.68</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>135.67</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>139.68</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>135.67</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>60058137.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>86773574.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>86773574.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>150795341.4</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>98002722.3</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>98002722.3</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-11994226.77350551</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>60058137</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>60058137.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>140.4</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>139.07</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>135.65</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>139.07</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>135.65</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>90013453.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>97804699.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>97804699.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>150452404.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>97676525.22</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>97676525.22</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-8621237.70714359</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>90013453</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>90013453.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>140.7</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>138.5</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>135.63</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>135.63</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>70495175.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>97813083.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>97813083.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>149014535.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>97243189.58</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>97243189.58</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-6704278.69422856</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>70495175</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>70495175.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>141.5</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>138.05</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>135.71</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>138.05</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>135.71</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>105621547.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>114008753.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>114008753.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>153115643.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>96664928.76</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>96664928.76000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-1635083.222413212</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>105621547</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>105621547.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>15.54</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>17.18</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>17.18</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>1184.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>1062.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>1062.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>1275.8</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>2043.92</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>2043.92</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-138.6892330545629</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>1184</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1184.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>15.44</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>16.28</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>17.22</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>17.22</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>863.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1160.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>1160.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>1326.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>2109.66</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>2109.66</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-152.01003222452</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>863</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>863.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>15.47</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>16.39</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>17.29</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>17.29</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>670.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1300.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1300</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>1398.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>2121.18</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>2121.18</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-131.2179584592973</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>670</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>670.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>15.59</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>17.37</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>17.37</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1844.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1644.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>1644.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>1516.1</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>2137.92</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>2137.92</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-76.15006884971831</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1844</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1844.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>15.8</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>16.66</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>17.44</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>751.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>1462.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>1462.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>1441.7</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>2140.54</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>2140.54</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-120.5477240914011</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>751</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>751.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>15.94</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>16.75</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>17.5</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>1673.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1489.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1489.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1529.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>2206.54</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>2206.54</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-62.56052714768407</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>1673</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>1673.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>16.18</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>17.58</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>17.58</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1562.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1492.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1492.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1566.8</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>2205.02</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>2205.02</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-76.27308411567083</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1562</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1562.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>16.28</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>17.65</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>2392.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1497.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>1497.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1678.6</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>2216.66</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>2216.66</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-81.2455553515208</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>2392</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2392.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>16.3</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>17.01</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>17.71</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>17.71</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>936.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>1387.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>1387.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1642.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>2251.76</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>2251.76</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-174.3760301401805</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>936</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>936.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>16.34</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>17.06</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>17.76</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>17.76</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>883.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1420.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1420.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1689.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>2307.24</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>2307.24</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-145.1918501904024</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>883</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>883.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>16.35</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>17.12</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>17.82</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>17.82</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>1691.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1569.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1569.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1696.7</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>2336.46</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>2336.46</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-92.63616989820503</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>1691</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1691.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>34.09</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>38.49</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>36.74</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>36.74</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>21966.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>23032.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>23032.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>24279.5</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>44047.4</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>44047.4</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-3295.996856766917</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>21966</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>21966.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>35.02</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>39.06</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>39.06</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>36.61</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>33464.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>21269.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>21269.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>25582.2</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>44082.68</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>44082.68</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-3451.276446698208</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>33464</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>33464.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>35.92999999999999</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>39.61</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>36.48</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>39.61</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>36.48</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>17834.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>17700.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>17700</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>23874.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>43670.22</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>43670.22</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-4781.773130646547</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>17834</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>17834.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>36.54</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>40.1</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>36.33</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>36.33</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>23097.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>21488.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>21488.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>25652.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>43784.08</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>43784.08</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-4837.062210192507</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>23097</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>23097.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>36.73</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>40.58</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>36.12</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>36.12</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>18802.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>24990.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>24990.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>26525.1</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>43596.94</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>43596.94</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-5307.187244894154</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>18802</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>18802.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>37.56</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>41.02</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>35.91</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>35.91</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>13149.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>25526.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>25526.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>29996.6</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>43534.98</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>43534.98</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-5329.073464293142</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>13149</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>13149.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>37.8</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>41.41</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>35.64</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>35.64</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>15618.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>29895.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>29895.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>32582.2</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>43919.34</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>43919.34</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-4564.336868281222</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>15618</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>15618.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>38.29000000000001</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>41.68</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>35.4</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>35.4</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>36775.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>30048.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>30048.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>33103.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>44116.8</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>44116.8</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-3573.379700111291</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>36775</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>36775.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>38.91</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>41.98</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>35.11</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>35.11</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>40607.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>29817.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>29817.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>34212.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>43720.24</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>43720.24</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-4296.927327721707</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>40607</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>40607.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>39.61</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>42.37</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>34.81</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>34.81</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>21483.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>28060.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>28060</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>32682.4</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>43193.14</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>43193.14</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-5587.676534032238</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>21483</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>21483.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>39.59</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>42.45</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>34.45</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>34993.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>34466.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>34466.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>34076.5</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>43412.38</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>43412.38</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-5183.044095403275</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>34993</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>34993.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>13.3</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>14.19</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>15</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>1994334.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>3089589.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>3089589.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>4951293.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>6472353.44</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>6472353.44</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-754541.438409226</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>1994334</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>1994334.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>13.2</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>15.02</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>2887931.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>4015602.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>4015602.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>5312006.6</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>6668359.22</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>6668359.22</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-636984.3126417883</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>2887931</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>2887931.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>13.26</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>15.06</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>3820644.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>4873892.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>4873892.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>5647568.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>6766459.28</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>6766459.28</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-542038.6575225266</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>3820644</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>3820644.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>13.43</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>14.54</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>15.11</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>15.11</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>3753951.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>5370945.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>5370945.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>5498368.9</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>6862839.6</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>6862839.6</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-486977.0195834916</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>3753951</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>3753951.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,21 +16967,17 @@
           <t>13.68</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>14.67</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
+      <c r="AM39" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="AO39" t="inlineStr">
         <is>
           <t>15.17</t>
         </is>
       </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>15.17</t>
-        </is>
-      </c>
       <c r="AP39" t="inlineStr">
         <is>
           <t>-45.11</t>
@@ -17244,20 +17018,16 @@
           <t>2991087.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>5758701.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>5758701</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>5444352.3</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>6953191.82</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>6953191.82</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-383779.8218283169</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>2991087</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>2991087.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>13.99</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>14.81</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>15.22</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>15.22</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>6624401.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>6812997.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>6812997.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>5408016.7</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>6998126.14</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>6998126.14</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-140913.4028270561</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>6624401</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>6624401.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>14.32</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>14.95</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>15.27</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>15.27</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>7179380.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>6608410.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>6608410.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>5307056.0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>7081144.12</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>7081144.12</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-178212.3970100041</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>7179380</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>7179380.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>14.49</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>15.32</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>15.32</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>6305908.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>6421244.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>6421244.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>5671035.4</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>7090922.8</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>7090922.8</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-284593.9816638576</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>6305908</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>6305908.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>14.54</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>15.13</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>15.36</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>15.36</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>5692729.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>5625792.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>5625792.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>5739229.6</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>7327484.66</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>7327484.66</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-332817.3175385091</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>5692729</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>5692729.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>14.56</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>15.18</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>15.4</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>8262569.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>5130003.6</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>5130003.6</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>6309728.4</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>8715517.68</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>8715517.68</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-324123.7145902077</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>8262569</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>8262569.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>14.48</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>15.45</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>5601466.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>4003036.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>4003036</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>7798552.9</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>9148653.16</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>9148653.16</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-575468.4348572707</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>5601466</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>5601466.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>47.45999999999999</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>46.71</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>45.01</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>45.01</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>93.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>139</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>165.9</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>0</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-92.25678478510804</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>93</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>47.58</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>46.6</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>44.96</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>44.96</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>113.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>184.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>184.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>186.8</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>0</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-92.38871133354613</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>113</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>47.58</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>46.42</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>44.88</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>46.42</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>44.88</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>96.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>181</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>181.3</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>0</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-91.42043814083098</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>96</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>47.46</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>46.24</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>44.83</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>44.83</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>150.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>182.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>182</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>243.4</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>0</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-84.95074650335113</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>150</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>47.71</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>45.98</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>44.8</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>44.8</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>243.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>181.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>181.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>539.5</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>0</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-78.46008893183159</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>243</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>48.07000000000001</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>45.79</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>44.73</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>44.73</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>320.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>192.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>192.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>844.0</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>0</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-76.3498606535241</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>320</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>48.52</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>45.66</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>44.67</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>44.67</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>96.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>189.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>189.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>819.5</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>0</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-78.85846808974463</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>96</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>48.72</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>45.51</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>44.59</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>45.51</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>44.59</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>101.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>181.6</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>181.6</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>814.5</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>0</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-55.62581913828308</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>101</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>48.85000000000001</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>44.53</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>44.53</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>147.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>304.8</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>304.8</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>827.6</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>0</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-20.98539852411352</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>147</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>48.55</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>44.97</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>44.46</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>44.46</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>300.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>897.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>897.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>828.0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>0</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>24.32182372913269</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>300</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>47.87</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>44.72</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>44.38</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>44.38</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>302.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>1495.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>1495.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>807.8</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>0</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>71.7849332434439</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>302</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>302.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24851,11 +24521,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
           <t>2459</t>
@@ -25037,41 +24703,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
+      <c r="AM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO57" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT57" t="inlineStr">
         <is>
           <t>0</t>
@@ -25092,20 +24754,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>0</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>0</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24780,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>0</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24949,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25133,11 @@
           <t>23.63</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>24.42</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>26.01</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>26.01</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25184,16 @@
           <t>69398365.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>46175655.8</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>46175655.8</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>40727993.5</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>194676121.56</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>194676121.56</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25210,10 @@
           <t>-6011750.455637693</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>69398365</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>69398365.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25379,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25563,11 @@
           <t>23.42</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>24.49</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25614,16 @@
           <t>40606624.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>40014316.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>40014316.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>41687883.7</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>195169236.84</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>195169236.84</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25640,10 @@
           <t>-9065902.528399438</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>40606624</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>40606624.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25809,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25993,11 @@
           <t>23.48</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>25.97</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>25.97</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26044,16 @@
           <t>33681849.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>39637812.8</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>39637812.8</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>51965661.4</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>195984000.1</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>195984000.1</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26070,10 @@
           <t>-10020365.29204483</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>33681849</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>33681849.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26239,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26423,11 @@
           <t>23.88</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>24.85</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26474,16 @@
           <t>49106509.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>38566967.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>38566967.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>52615128.9</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>195992723.02</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>195992723.02</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26500,10 @@
           <t>-10284073.15825091</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>49106509</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>49106509.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26669,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26853,11 @@
           <t>24.26</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26904,16 @@
           <t>38084932.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>35331650.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>35331650.4</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>52705529.4</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>195762947.24</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>195762947.24</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26930,10 @@
           <t>-11946152.49717921</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>38084932</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>38084932.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27099,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27283,11 @@
           <t>24.53</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>25.95</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27334,16 @@
           <t>38591667.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>35280331.2</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>35280331.2</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>51774555.3</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>196053683.56</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>196053683.56</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27360,10 @@
           <t>-12713019.99932038</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>38591667</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>38591667.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27529,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27713,11 @@
           <t>25.11</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>25.96</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>25.96</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27764,16 @@
           <t>38724107.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>43361451.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>43361451.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>53384515.1</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>197488634.64</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>197488634.64</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27790,10 @@
           <t>-13408801.60954632</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>38724107</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>38724107.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27959,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28143,11 @@
           <t>25.59</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>25.56</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>25.94</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>25.94</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28194,16 @@
           <t>28327621.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>64293510.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>64293510</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>53134957.6</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>197699079.6</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>197699079.6</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28220,10 @@
           <t>-13938079.56667101</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>28327621</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>28327621.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28389,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28573,11 @@
           <t>25.52</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>25.58</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>25.88</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>25.88</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28624,16 @@
           <t>32929925.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>66663290.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>66663290.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>54706545.9</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>197755621.26</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>197755621.26</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28650,10 @@
           <t>-13082493.16375375</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>32929925</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>32929925.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28819,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29003,11 @@
           <t>25.35</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>25.82</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29054,16 @@
           <t>37828336.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>70079408.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>70079408.40000001</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>58159640.7</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>197616845.6</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>197616845.6</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29080,10 @@
           <t>-11886098.97516645</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>37828336</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>37828336.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29249,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29433,11 @@
           <t>25.03</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>25.76</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>25.76</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29484,16 @@
           <t>78997267.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>68268779.4</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>68268779.40000001</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>64193506.3</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>197596036.22</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>197596036.22</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29510,10 @@
           <t>-10277290.63521439</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>78997267</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>78997267.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29679,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29863,11 @@
           <t>156.3</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>164.85</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>168.36</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>164.85</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>168.36</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29914,16 @@
           <t>3170553681.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>4138082091.0</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>4138082091</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>4268507640.2</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>6060043081.46</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>6060043081.46</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29940,10 @@
           <t>-263552895.6884155</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>3170553681</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>3170553681.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30109,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30293,11 @@
           <t>155.3</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>166.68</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>168.5</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>166.68</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>168.5</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30344,16 @@
           <t>3561255788.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>4508528303.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>4508528303.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>4128239206.8</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>6523283246.84</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>6523283246.84</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30370,10 @@
           <t>-197408387.5697174</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>3561255788</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>3561255788.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30539,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30723,11 @@
           <t>155.3</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>168.38</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>168.5</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>168.38</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>168.5</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30774,16 @@
           <t>5330763891.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>5326173063.4</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>5326173063.4</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>4050371893.2</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>6516029437.64</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>6516029437.64</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30800,10 @@
           <t>-137726873.5940866</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>5330763891</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>5330763891.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30969,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31153,11 @@
           <t>156.8</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>169.72</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>168.21</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>169.72</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>168.21</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31204,16 @@
           <t>3892624091.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>4843786138.2</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>4843786138.2</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>3728171837.0</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>6576214335.28</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>6576214335.28</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31230,10 @@
           <t>-237138904.8933973</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>3892624091</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>3892624091.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31399,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31583,11 @@
           <t>158.6</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>170.58</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>167.82</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>170.58</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>167.82</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31634,16 @@
           <t>4735213004.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>4739633072.6</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>4739633072.6</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>3540693680.5</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>6556873375.6</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>6556873375.6</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31660,10 @@
           <t>-216600438.7176485</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>4735213004</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>4735213004.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31829,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32013,11 @@
           <t>159.5</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>170.95</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>167.23</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>170.95</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>167.23</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32064,16 @@
           <t>5022784742.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>4398933189.4</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>4398933189.4</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>3348452263.6</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>6518094899.78</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>6518094899.78</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32090,10 @@
           <t>-269801426.3338051</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>5022784742</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>5022784742.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32259,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32443,11 @@
           <t>162.1</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>171.55</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>166.67</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>171.55</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>166.67</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32494,16 @@
           <t>7649479589.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>3747950110.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>3747950110.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>3187753716.9</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>6448828659.12</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>6448828659.12</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32520,10 @@
           <t>-366978329.6306791</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>7649479589</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>7649479589.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32689,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32873,11 @@
           <t>164.7</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>172.05</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>166.08</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>172.05</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>166.08</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32924,16 @@
           <t>2918829265.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>2774570723.0</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>2774570723</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>3016948267.5</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>6307955645.82</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>6307955645.82</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32950,10 @@
           <t>-774127699.0322614</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>2918829265</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>2918829265.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33119,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33303,11 @@
           <t>166.0</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>172.2</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>165.33</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>165.33</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33354,16 @@
           <t>3371858763.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>2612557535.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>2612557535.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>3246709810.3</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>6279997636.12</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>6279997636.12</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33380,10 @@
           <t>-821266845.6405125</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>3371858763</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>3371858763.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33549,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33733,11 @@
           <t>166.8</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>172.52</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>164.6</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>172.52</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>164.6</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33784,16 @@
           <t>3031713588.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>2341754288.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>2341754288.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>3717183320.3</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>6247764195.28</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>6247764195.28</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33810,10 @@
           <t>-907816399.6651387</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>3031713588</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>3031713588.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33979,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34163,11 @@
           <t>167.7</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>172.38</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>163.91</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>172.38</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>163.91</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34214,16 @@
           <t>1767869347.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>2297971337.8</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>2297971337.8</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>5310238320.6</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>6248161668.22</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>6248161668.22</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34240,10 @@
           <t>-962592479.5337062</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>1767869347</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>1767869347.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34409,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34593,11 @@
           <t>59.16</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>58.96</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>59.73</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>59.73</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34644,16 @@
           <t>178713.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>179531.8</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>179531.8</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>507219.1</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>568785.08</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>568785.08</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34670,10 @@
           <t>-130240.1653460538</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>178713</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>178713.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34839,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35023,11 @@
           <t>58.91999999999999</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>58.92</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>59.75</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>58.92</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>59.75</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35074,16 @@
           <t>59368.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>167448.4</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>167448.4</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>536549.6</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>573742.92</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>573742.92</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35100,10 @@
           <t>-127139.9301351309</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>59368</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>59368.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35269,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35453,11 @@
           <t>58.8</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>58.92</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>59.78</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>58.92</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>59.78</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35504,16 @@
           <t>176600.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>397966.4</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>397966.4</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>671278.2</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>588239.56</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>588239.5600000001</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35530,10 @@
           <t>-105383.3466147005</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>176600</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>176600.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35699,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35883,11 @@
           <t>58.6</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>58.96</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>59.81</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>59.81</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35934,16 @@
           <t>424178.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>675022.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>675022</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>659538.2</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>585917.56</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>585917.5600000001</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35960,10 @@
           <t>-83099.39349213219</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>424178</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>424178.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36129,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36313,11 @@
           <t>58.44</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>58.99</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>59.85</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>59.85</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36364,16 @@
           <t>58800.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>752886.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>752886.4</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>693870.4</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>597036.1</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>597036.1</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36390,10 @@
           <t>-74823.55354945839</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>58800</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>58800.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36559,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36743,11 @@
           <t>58.38000000000001</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>59.05</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>59.89</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>59.89</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36794,16 @@
           <t>118296.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>834906.4</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>834906.4</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>755818.3</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>599506.1</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>599506.1</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36820,10 @@
           <t>-21181.01243315812</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>118296</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>118296.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36989,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37173,11 @@
           <t>58.42</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>59.11</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>59.93</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>59.93</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37224,16 @@
           <t>1211958.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>905650.8</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>905650.8</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>826030.3</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>610527.46</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>610527.46</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37250,10 @@
           <t>49833.08246274071</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>1211958</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>1211958.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37419,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37603,11 @@
           <t>58.3</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>59.19</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>59.96</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>59.96</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37654,16 @@
           <t>1561878.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>944590.0</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>944590</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>746274.5</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>595958.3</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>595958.3</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37680,10 @@
           <t>32323.96508321259</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>1561878</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>1561878.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37849,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38033,11 @@
           <t>58.54</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>59.3</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>60.01</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>60.01</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38084,16 @@
           <t>813500.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>644054.4</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>644054.4</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>860382.6</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>565926.74</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>565926.74</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38110,10 @@
           <t>-31334.91564051376</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>813500</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>813500.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38279,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38463,11 @@
           <t>58.73999999999999</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>59.42</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>60.07</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>59.42</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>60.07</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38514,16 @@
           <t>468900.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>634854.4</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>634854.4</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>850602.6</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>555736.74</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>555736.74</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38540,10 @@
           <t>-40973.71254439012</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>468900</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>468900.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38709,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38893,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>59.52</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>59.52</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>60.11</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38944,16 @@
           <t>472018.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>676730.2</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>676730.2</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>1057342.6</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>564385.12</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>564385.12</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38970,10 @@
           <t>-16358.64695905661</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>472018</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>472018.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39139,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39323,11 @@
           <t>49.95</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>50.13</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>47.19</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>47.19</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39374,16 @@
           <t>2760254.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>2489543.8</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>2489543.8</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>2608342.2</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>2056931.92</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>2056931.92</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39400,10 @@
           <t>116547.446286709</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>2760254</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>2760254.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39569,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39753,11 @@
           <t>49.95</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>50.11</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>47.05</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>47.05</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39804,16 @@
           <t>2576995.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>2361328.0</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>2361328</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>2573029.5</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>2029667.66</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>2029667.66</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39830,10 @@
           <t>110121.6442078613</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>2576995</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>2576995.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +39999,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40183,11 @@
           <t>50.03</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>50.11</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>46.92</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>46.92</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40234,16 @@
           <t>3563323.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>2348089.0</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>2348089</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>2549300.0</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>1995061.6</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>1995061.6</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40260,10 @@
           <t>116643.9039449403</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>3563323</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>3563323.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40429,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40613,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>50.08</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>46.78</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>46.78</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40664,16 @@
           <t>1902947.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>2333703.0</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>2333703</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>2385178.1</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>1930653.14</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>1930653.14</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40690,10 @@
           <t>16117.56414273381</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>1902947</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>1902947.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40859,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41043,11 @@
           <t>49.8</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>50.01</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>46.64</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>46.64</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41094,16 @@
           <t>1644200.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>2577326.8</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>2577326.8</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>2288006.9</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>1901183.2</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>1901183.2</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41120,10 @@
           <t>49830.30856305594</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>1644200</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>1644200.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41289,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41473,11 @@
           <t>49.74</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>49.96</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>46.51</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>49.96</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>46.51</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41524,16 @@
           <t>2119175.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>2727140.6</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>2727140.6</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>2257097.1</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>1875176.74</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>1875176.74</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41550,10 @@
           <t>123934.6110005495</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>2119175</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>2119175.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41719,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41903,11 @@
           <t>49.74</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>49.92</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>46.37</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>46.37</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41954,16 @@
           <t>2510800.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>2784731.0</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>2784731</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>2228150.6</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>1847608.44</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>1847608.44</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41980,10 @@
           <t>174481.4855183777</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>2510800</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>2510800.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42149,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42333,11 @@
           <t>49.57</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>49.86</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>46.23</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>46.23</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42384,16 @@
           <t>3491393.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>2750511.0</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>2750511</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>2348177.7</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>1840232.42</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>1840232.42</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42410,10 @@
           <t>198500.0032039052</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>3491393</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>3491393.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42579,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42763,11 @@
           <t>49.57</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>46.11</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>46.11</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42814,16 @@
           <t>3121066.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>2436653.2</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>2436653.2</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>2112008.7</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>1822330.06</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>1822330.06</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42840,10 @@
           <t>120659.3497830899</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>3121066</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>3121066.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43009,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43193,11 @@
           <t>49.93000000000001</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>46</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43244,16 @@
           <t>2393269.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>1998687.0</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>1998687</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>2008014.5</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>1802662.46</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>1802662.46</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43270,10 @@
           <t>44827.0466896724</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>2393269</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>2393269.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43439,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43623,11 @@
           <t>50.29</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>49.67</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>45.89</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>45.89</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43674,16 @@
           <t>2407127.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>1787053.6</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>1787053.6</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>1879214.6</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>1779185.08</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>1779185.08</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43700,10 @@
           <t>12872.46917444491</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>2407127</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>2407127.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43869,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44053,11 @@
           <t>35.61</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>36.04</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>33.85</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44104,16 @@
           <t>10003939.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>16812721.4</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>16812721.4</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>28955598.5</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>37495260.14</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>37495260.14</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44130,10 @@
           <t>-4963789.006092828</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>10003939</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>10003939.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44299,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44483,11 @@
           <t>35.49</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>33.64</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44534,16 @@
           <t>16335914.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>24791136.2</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>24791136.2</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>29744586.4</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>37462800.8</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>37462800.8</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44560,10 @@
           <t>-4227662.37471519</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>16335914</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>16335914.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44729,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44913,11 @@
           <t>35.94</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>36.29</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>33.43</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>36.29</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>33.43</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44964,16 @@
           <t>11426356.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>28405642.0</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>28405642</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>30635525.9</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>37276453.84</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>37276453.84</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44990,10 @@
           <t>-3703490.852221593</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>11426356</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>11426356.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45159,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45343,11 @@
           <t>36.5</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>36.41</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>33.23</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>36.41</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>33.23</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45394,16 @@
           <t>23070340.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>40583749.8</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>40583749.8</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>31288459.2</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>37153017.02</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>37153017.02</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45420,10 @@
           <t>-2296382.789651394</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>23070340</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>23070340.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45589,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45773,11 @@
           <t>36.73</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>36.54</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>33.05</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45824,16 @@
           <t>23227058.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>39483592.2</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>39483592.2</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>32054656.6</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>36851291.98</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>36851291.98</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45850,10 @@
           <t>-1451784.457777843</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>23227058</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>23227058.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46019,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46203,11 @@
           <t>36.55</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>32.83</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>32.83</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46254,16 @@
           <t>49896013.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>41098475.6</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>41098475.6</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>35111442.6</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>36487231.22</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>36487231.22</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46280,10 @@
           <t>-210157.1816092804</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>49896013</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>49896013.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46449,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46633,11 @@
           <t>36.48</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>36.7</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>32.65</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46684,16 @@
           <t>34408443.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>34698036.6</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>34698036.6</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>33253068.6</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>35584667.3</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>35584667.3</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46710,10 @@
           <t>-1286286.352025293</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>34408443</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>34408443.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46879,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47063,11 @@
           <t>35.92</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>36.71</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>32.41</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>32.41</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47114,16 @@
           <t>72316895.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>32865409.8</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>32865409.8</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>37547059.9</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>35339260.36</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>35339260.36</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47140,10 @@
           <t>-1118292.440047257</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>72316895</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>72316895.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47309,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47493,11 @@
           <t>35.37</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>36.63</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>32.15</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47544,16 @@
           <t>17569552.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>21993168.6</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>21993168.6</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>35485008.4</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>34069635.44</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>34069635.44</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47570,10 @@
           <t>-4899981.978648372</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>17569552</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>17569552.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47739,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47923,11 @@
           <t>35.11</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>36.68</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>31.93</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>31.93</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47974,16 @@
           <t>31301475.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>24625721.0</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>24625721</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>38550535.3</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>33946568.62</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>33946568.62</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48000,10 @@
           <t>-4261609.498841092</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>31301475</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>31301475.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48169,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48353,11 @@
           <t>35.06</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>36.67</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>31.73</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>31.73</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48404,16 @@
           <t>17893818.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>29124409.6</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>29124409.6</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>39927956.0</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>33607601.62</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>33607601.62</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48430,10 @@
           <t>-4668725.938443527</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>17893818</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>17893818.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48599,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48783,11 @@
           <t>24.44</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>25.48</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>25.91</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>25.91</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48834,16 @@
           <t>539777.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>264273.0</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>264273</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>0</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48860,10 @@
           <t>44881.51406765514</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>539777</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>539777.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49029,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49213,11 @@
           <t>24.64</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>25.54</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>25.96</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>25.96</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49264,16 @@
           <t>506472.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>0</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>0</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49290,10 @@
           <t>22415.69480793941</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>506472</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>506472.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49459,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49643,11 @@
           <t>24.92</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>26.02</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>26.02</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49694,16 @@
           <t>118514.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>0</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>0</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49720,10 @@
           <t>-6910.500377652337</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>118514</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>118514.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49889,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50073,11 @@
           <t>25.24</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>26.07</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>26.07</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50124,16 @@
           <t>24600.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>0</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>0</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50150,10 @@
           <t>-6991.332772152935</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>24600</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>24600.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50319,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50503,11 @@
           <t>25.56</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>25.74</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>26.11</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>26.11</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50554,16 @@
           <t>132002.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>0</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>0</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50580,10 @@
           <t>3205.097120423074</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>132002</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>132002.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50749,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50933,11 @@
           <t>25.61</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>26.14</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>26.14</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50984,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>0</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>0</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51010,10 @@
           <t>7191.902127247391</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>0</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51179,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51363,11 @@
           <t>25.68</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>25.8</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>26.16</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>26.16</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51414,16 @@
           <t>28555.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>195176.0</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>195176</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>184695.0</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>0</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51440,10 @@
           <t>7191.902127247391</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>28555</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>28555.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51609,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51793,11 @@
           <t>25.74</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>26.2</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>26.2</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51844,16 @@
           <t>239420.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>194500.4</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>194500.4</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>182076.2</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>0</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51870,10 @@
           <t>22566.6290206922</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>239420</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>239420.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52039,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52223,11 @@
           <t>25.74</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>25.84</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>26.22</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>26.22</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52274,16 @@
           <t>367406.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>192291.2</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>192291.2</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>170174.7</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>0</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52300,10 @@
           <t>21131.89497487433</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>367406</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>367406.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52469,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52653,11 @@
           <t>25.64</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>25.83</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>26.23</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>26.23</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52704,16 @@
           <t>12180.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>182809.6</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>182809.6</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>142589.0</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>0</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52730,10 @@
           <t>4614.778660317592</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>12180</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>12180.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52899,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53083,11 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>25.84</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>26.26</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>26.26</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53134,16 @@
           <t>328319.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>181039.0</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>181039</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>149562.6</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>0</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53160,10 @@
           <t>18914.01325879659</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>328319</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>328319.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53329,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53513,11 @@
           <t>47.91</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>47.38</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>44.94</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>47.38</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>44.94</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53564,16 @@
           <t>65500452.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>94097787.2</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>94097787.2</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>92792972.5</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>105693348.54</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>105693348.54</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53590,10 @@
           <t>-11426547.73089139</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>65500452</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>65500452.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53759,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53943,11 @@
           <t>47.73999999999999</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>47.44</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>44.81</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>44.81</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53994,16 @@
           <t>43170824.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>94507684.4</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>94507684.40000001</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>96300582.7</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>109219533.0</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>109219533</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54020,10 @@
           <t>-9739743.421501234</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>43170824</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>43170824.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54189,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54373,11 @@
           <t>47.55</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>47.54</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>44.68</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>44.68</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54424,16 @@
           <t>223761896.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>98580928.2</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>98580928.2</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>109219552.1</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>108910027.54</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>108910027.54</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54450,10 @@
           <t>-4589714.857318833</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>223761896</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>223761896.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54619,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54803,11 @@
           <t>47.51</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>44.55</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>44.55</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54854,16 @@
           <t>71340321.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>77890233.4</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>77890233.40000001</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>94676515.8</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>104919533.28</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>104919533.28</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54880,10 @@
           <t>-16417656.23501115</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>71340321</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>71340321.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55049,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55233,11 @@
           <t>47.53</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>47.64</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>44.44</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>47.64</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>44.44</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55284,16 @@
           <t>66715443.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>85834375.4</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>85834375.40000001</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>108740825.8</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>104375946.34</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>104375946.34</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55310,10 @@
           <t>-16397487.44474977</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>66715443</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>66715443.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55479,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55663,11 @@
           <t>47.53</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>47.61</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>44.3</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>47.61</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>44.3</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55714,16 @@
           <t>67549938.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>91488157.8</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>91488157.8</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>120764151.7</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>103367070.76</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>103367070.76</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55740,10 @@
           <t>-15287527.69277819</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>67549938</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>67549938.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55909,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56093,11 @@
           <t>47.38</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>47.49</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>44.16</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>47.49</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>44.16</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56144,16 @@
           <t>63537043.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>98093481.0</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>98093481</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>129910085.4</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>102345535.14</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>102345535.14</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56170,10 @@
           <t>-13245297.95093384</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>63537043</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>63537043.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56339,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56523,11 @@
           <t>47.42999999999999</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>47.31</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>44.03</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>44.03</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56574,16 @@
           <t>120308422.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>119858176.0</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>119858176</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>129167287.6</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>101365787.6</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>101365787.6</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56600,10 @@
           <t>-9424827.500051439</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>120308422</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>120308422.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56769,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56953,11 @@
           <t>46.62</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>47.07</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>43.88</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>43.88</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57004,16 @@
           <t>111061031.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>111462798.2</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>111462798.2</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>125114691.2</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>99327479.0</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>99327479</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57030,10 @@
           <t>-9713059.338074729</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>111061031</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>111061031.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57199,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57383,11 @@
           <t>46.15</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>46.83</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>43.74</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>46.83</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>43.74</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57434,16 @@
           <t>94984355.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>131647276.2</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>131647276.2</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>124179002.4</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>97696560.32</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>97696560.31999999</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57460,10 @@
           <t>-8787132.237462461</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>94984355</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>94984355.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
@@ -58425,7 +57629,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -58609,15 +57813,11 @@
           <t>46.29</t>
         </is>
       </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>46.54</t>
-        </is>
-      </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>43.61</t>
-        </is>
+      <c r="AM134" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>43.61</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -58664,20 +57864,16 @@
           <t>100576554.0</t>
         </is>
       </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>150040145.6</t>
-        </is>
+      <c r="AX134" t="n">
+        <v>150040145.6</v>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
           <t>136005740.8</t>
         </is>
       </c>
-      <c r="AZ134" t="inlineStr">
-        <is>
-          <t>96471183.3</t>
-        </is>
+      <c r="AZ134" t="n">
+        <v>96471183.3</v>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
@@ -58694,8 +57890,10 @@
           <t>-5428052.085249841</t>
         </is>
       </c>
-      <c r="BD134" t="n">
-        <v>100576554</v>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>100576554.0</t>
+        </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
@@ -58861,7 +58059,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -59045,15 +58243,11 @@
           <t>24.31</t>
         </is>
       </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>24.62</t>
-        </is>
-      </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>24.88</t>
-        </is>
+      <c r="AM135" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>24.88</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -59100,20 +58294,16 @@
           <t>853788.0</t>
         </is>
       </c>
-      <c r="AX135" t="inlineStr">
-        <is>
-          <t>352599.6</t>
-        </is>
+      <c r="AX135" t="n">
+        <v>352599.6</v>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
           <t>513834.1</t>
         </is>
       </c>
-      <c r="AZ135" t="inlineStr">
-        <is>
-          <t>549902.74</t>
-        </is>
+      <c r="AZ135" t="n">
+        <v>549902.74</v>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
@@ -59130,8 +58320,10 @@
           <t>-6290.655351946014</t>
         </is>
       </c>
-      <c r="BD135" t="n">
-        <v>853788</v>
+      <c r="BD135" t="inlineStr">
+        <is>
+          <t>853788.0</t>
+        </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
@@ -59297,7 +58489,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -59481,15 +58673,11 @@
           <t>24.21</t>
         </is>
       </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>24.65</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>24.89</t>
-        </is>
+      <c r="AM136" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>24.89</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -59536,20 +58724,16 @@
           <t>196789.0</t>
         </is>
       </c>
-      <c r="AX136" t="inlineStr">
-        <is>
-          <t>244948.6</t>
-        </is>
+      <c r="AX136" t="n">
+        <v>244948.6</v>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
           <t>523130.2</t>
         </is>
       </c>
-      <c r="AZ136" t="inlineStr">
-        <is>
-          <t>550001.94</t>
-        </is>
+      <c r="AZ136" t="n">
+        <v>550001.9399999999</v>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
@@ -59566,8 +58750,10 @@
           <t>-47069.49763949629</t>
         </is>
       </c>
-      <c r="BD136" t="n">
-        <v>196789</v>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>196789.0</t>
+        </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
@@ -59733,7 +58919,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -59917,15 +59103,11 @@
           <t>24.19</t>
         </is>
       </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>24.93</t>
-        </is>
+      <c r="AM137" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>24.93</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
@@ -59972,20 +59154,16 @@
           <t>400007.0</t>
         </is>
       </c>
-      <c r="AX137" t="inlineStr">
-        <is>
-          <t>409310.4</t>
-        </is>
+      <c r="AX137" t="n">
+        <v>409310.4</v>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
           <t>509151.5</t>
         </is>
       </c>
-      <c r="AZ137" t="inlineStr">
-        <is>
-          <t>565795.96</t>
-        </is>
+      <c r="AZ137" t="n">
+        <v>565795.96</v>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
@@ -60002,8 +59180,10 @@
           <t>-33251.18313458608</t>
         </is>
       </c>
-      <c r="BD137" t="n">
-        <v>400007</v>
+      <c r="BD137" t="inlineStr">
+        <is>
+          <t>400007.0</t>
+        </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
@@ -60169,7 +59349,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -60353,21 +59533,17 @@
           <t>24.24</t>
         </is>
       </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>24.72</t>
-        </is>
-      </c>
-      <c r="AN138" t="inlineStr">
+      <c r="AM138" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="AO138" t="inlineStr">
         <is>
           <t>24.96</t>
         </is>
       </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>24.96</t>
-        </is>
-      </c>
       <c r="AP138" t="inlineStr">
         <is>
           <t>-60.84</t>
@@ -60408,20 +59584,16 @@
           <t>93197.0</t>
         </is>
       </c>
-      <c r="AX138" t="inlineStr">
-        <is>
-          <t>622685.6</t>
-        </is>
+      <c r="AX138" t="n">
+        <v>622685.6</v>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
           <t>487775.8</t>
         </is>
       </c>
-      <c r="AZ138" t="inlineStr">
-        <is>
-          <t>593356.14</t>
-        </is>
+      <c r="AZ138" t="n">
+        <v>593356.14</v>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
@@ -60438,8 +59610,10 @@
           <t>-34096.54872990778</t>
         </is>
       </c>
-      <c r="BD138" t="n">
-        <v>93197</v>
+      <c r="BD138" t="inlineStr">
+        <is>
+          <t>93197.0</t>
+        </is>
       </c>
       <c r="BE138" t="inlineStr">
         <is>
@@ -60605,7 +59779,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -60789,15 +59963,11 @@
           <t>24.38</t>
         </is>
       </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>24.76</t>
-        </is>
-      </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
+      <c r="AM139" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>25</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -60844,20 +60014,16 @@
           <t>219217.0</t>
         </is>
       </c>
-      <c r="AX139" t="inlineStr">
-        <is>
-          <t>635020.4</t>
-        </is>
+      <c r="AX139" t="n">
+        <v>635020.4</v>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
           <t>508678.4</t>
         </is>
       </c>
-      <c r="AZ139" t="inlineStr">
-        <is>
-          <t>964260.78</t>
-        </is>
+      <c r="AZ139" t="n">
+        <v>964260.78</v>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
@@ -60874,8 +60040,10 @@
           <t>-1213.979982870631</t>
         </is>
       </c>
-      <c r="BD139" t="n">
-        <v>219217</v>
+      <c r="BD139" t="inlineStr">
+        <is>
+          <t>219217.0</t>
+        </is>
       </c>
       <c r="BE139" t="inlineStr">
         <is>
@@ -61041,7 +60209,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -61225,15 +60393,11 @@
           <t>24.5</t>
         </is>
       </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>24.79</t>
-        </is>
-      </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>25.01</t>
-        </is>
+      <c r="AM140" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>25.01</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -61280,20 +60444,16 @@
           <t>315533.0</t>
         </is>
       </c>
-      <c r="AX140" t="inlineStr">
-        <is>
-          <t>675068.6</t>
-        </is>
+      <c r="AX140" t="n">
+        <v>675068.6</v>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
           <t>514077.4</t>
         </is>
       </c>
-      <c r="AZ140" t="inlineStr">
-        <is>
-          <t>974097.9</t>
-        </is>
+      <c r="AZ140" t="n">
+        <v>974097.9</v>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
@@ -61310,8 +60470,10 @@
           <t>32302.33179799921</t>
         </is>
       </c>
-      <c r="BD140" t="n">
-        <v>315533</v>
+      <c r="BD140" t="inlineStr">
+        <is>
+          <t>315533.0</t>
+        </is>
       </c>
       <c r="BE140" t="inlineStr">
         <is>
@@ -61477,7 +60639,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -61661,15 +60823,11 @@
           <t>24.7</t>
         </is>
       </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>24.82</t>
-        </is>
-      </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>25.03</t>
-        </is>
+      <c r="AM141" t="n">
+        <v>24.82</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>25.03</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -61716,20 +60874,16 @@
           <t>1018598.0</t>
         </is>
       </c>
-      <c r="AX141" t="inlineStr">
-        <is>
-          <t>801311.8</t>
-        </is>
+      <c r="AX141" t="n">
+        <v>801311.8</v>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
           <t>542011.0</t>
         </is>
       </c>
-      <c r="AZ141" t="inlineStr">
-        <is>
-          <t>1005372.32</t>
-        </is>
+      <c r="AZ141" t="n">
+        <v>1005372.32</v>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
@@ -61746,8 +60900,10 @@
           <t>68709.55106359918</t>
         </is>
       </c>
-      <c r="BD141" t="n">
-        <v>1018598</v>
+      <c r="BD141" t="inlineStr">
+        <is>
+          <t>1018598.0</t>
+        </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
@@ -61913,7 +61069,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -62097,15 +61253,11 @@
           <t>24.84</t>
         </is>
       </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>24.85</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>25.04</t>
-        </is>
+      <c r="AM142" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>25.04</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -62152,20 +61304,16 @@
           <t>1466883.0</t>
         </is>
       </c>
-      <c r="AX142" t="inlineStr">
-        <is>
-          <t>608992.6</t>
-        </is>
+      <c r="AX142" t="n">
+        <v>608992.6</v>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
           <t>483155.2</t>
         </is>
       </c>
-      <c r="AZ142" t="inlineStr">
-        <is>
-          <t>987291.96</t>
-        </is>
+      <c r="AZ142" t="n">
+        <v>987291.96</v>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
@@ -62182,8 +61330,10 @@
           <t>42937.55890504201</t>
         </is>
       </c>
-      <c r="BD142" t="n">
-        <v>1466883</v>
+      <c r="BD142" t="inlineStr">
+        <is>
+          <t>1466883.0</t>
+        </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
@@ -62349,7 +61499,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -62533,15 +61683,11 @@
           <t>24.87</t>
         </is>
       </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>24.85</t>
-        </is>
-      </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>25.03</t>
-        </is>
+      <c r="AM143" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>25.03</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -62588,20 +61734,16 @@
           <t>154871.0</t>
         </is>
       </c>
-      <c r="AX143" t="inlineStr">
-        <is>
-          <t>352866.0</t>
-        </is>
+      <c r="AX143" t="n">
+        <v>352866</v>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
           <t>373488.4</t>
         </is>
       </c>
-      <c r="AZ143" t="inlineStr">
-        <is>
-          <t>967200.24</t>
-        </is>
+      <c r="AZ143" t="n">
+        <v>967200.24</v>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
@@ -62618,8 +61760,10 @@
           <t>-43443.59271093411</t>
         </is>
       </c>
-      <c r="BD143" t="n">
-        <v>154871</v>
+      <c r="BD143" t="inlineStr">
+        <is>
+          <t>154871.0</t>
+        </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
@@ -62785,7 +61929,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -62969,15 +62113,11 @@
           <t>24.85</t>
         </is>
       </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>24.84</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
+      <c r="AM144" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>25.02</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -63024,20 +62164,16 @@
           <t>419458.0</t>
         </is>
       </c>
-      <c r="AX144" t="inlineStr">
-        <is>
-          <t>382336.4</t>
-        </is>
+      <c r="AX144" t="n">
+        <v>382336.4</v>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
           <t>390871.7</t>
         </is>
       </c>
-      <c r="AZ144" t="inlineStr">
-        <is>
-          <t>966095.88</t>
-        </is>
+      <c r="AZ144" t="n">
+        <v>966095.88</v>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
@@ -63054,8 +62190,10 @@
           <t>-24720.96670836664</t>
         </is>
       </c>
-      <c r="BD144" t="n">
-        <v>419458</v>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>419458.0</t>
+        </is>
       </c>
       <c r="BE144" t="inlineStr">
         <is>
@@ -63221,7 +62359,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -63405,15 +62543,11 @@
           <t>24.78</t>
         </is>
       </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>24.81</t>
-        </is>
-      </c>
-      <c r="AN145" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
+      <c r="AM145" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>25.02</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -63460,20 +62594,16 @@
           <t>946749.0</t>
         </is>
       </c>
-      <c r="AX145" t="inlineStr">
-        <is>
-          <t>353086.2</t>
-        </is>
+      <c r="AX145" t="n">
+        <v>353086.2</v>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
           <t>405525.4</t>
         </is>
       </c>
-      <c r="AZ145" t="inlineStr">
-        <is>
-          <t>964838.46</t>
-        </is>
+      <c r="AZ145" t="n">
+        <v>964838.46</v>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
@@ -63490,8 +62620,10 @@
           <t>-25440.07360797143</t>
         </is>
       </c>
-      <c r="BD145" t="n">
-        <v>946749</v>
+      <c r="BD145" t="inlineStr">
+        <is>
+          <t>946749.0</t>
+        </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
